--- a/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploTiposDeProcesso.xlsx
+++ b/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploTiposDeProcesso.xlsx
@@ -134,7 +134,7 @@
     <t>Processo relacionado a desempenho.</t>
   </si>
   <si>
-    <t>23.155</t>
+    <t>023.155</t>
   </si>
   <si>
     <t>SBM;PEN</t>
@@ -359,7 +359,7 @@
     <t>Processo relacionado a constituição da comissão interna de prevenção de acidentes (cipa).</t>
   </si>
   <si>
-    <t>25.311</t>
+    <t>025.311</t>
   </si>
 </sst>
 </file>

--- a/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploTiposDeProcesso.xlsx
+++ b/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploTiposDeProcesso.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
   <si>
     <t>0.Seq</t>
   </si>
@@ -59,22 +59,16 @@
     <t>13.InternoDoSistema</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Comunicação: Serviço De Transmissão De Dados, Voz E Imagem</t>
   </si>
   <si>
     <t>Processo relacionado a serviço de transmissão de dados, voz e imagem.</t>
   </si>
   <si>
-    <t>073.4</t>
-  </si>
-  <si>
-    <t>PEN;SBM</t>
-  </si>
-  <si>
-    <t>PEN:ADMIN|NEG;SBM:GABPREF|SEDUC</t>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>ABC:GABIN|SEADM</t>
   </si>
   <si>
     <t>PUB;RES</t>
@@ -86,18 +80,12 @@
     <t>Protocolo Pendente de Análise de Restrição (Art. 6º, III, da Lei nº 12.527/2011)</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Gestão de Contrato: Cadastramento De Fornecedores E De Prestadores De Serviços</t>
   </si>
   <si>
     <t>Processo relacionado a cadastramento de fornecedores e de prestadores de serviços.</t>
   </si>
   <si>
-    <t>030.02</t>
-  </si>
-  <si>
     <t>PUB;RES;SIG</t>
   </si>
   <si>
@@ -110,37 +98,22 @@
     <t>Informação Pessoal Sensível (Art. 31 da Lei nº 12.527/2011)</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Capacitação: Contratação de curso com ônus à Instituição</t>
   </si>
   <si>
     <t>Processo relacionado a com ônus.</t>
   </si>
   <si>
-    <t>028.21</t>
-  </si>
-  <si>
     <t>PUB</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Pessoal: Avaliação de Desempenho</t>
   </si>
   <si>
     <t>Processo relacionado a desempenho.</t>
   </si>
   <si>
-    <t>023.155</t>
-  </si>
-  <si>
-    <t>SBM;PEN</t>
-  </si>
-  <si>
-    <t>SBM:GABPREF;PEN:ADMIN</t>
+    <t>ABC:GABIN</t>
   </si>
   <si>
     <t>Investigação/Prevenção de Acidentes Aeronáuticos (Art. 88-I, § 3º, da Lei nº 7.565/1986)</t>
@@ -149,198 +122,111 @@
     <t>SIM</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Pessoal: Emissão De Certificados</t>
   </si>
   <si>
     <t>Processo relacionado a emissão de certificados.</t>
   </si>
   <si>
-    <t>914</t>
-  </si>
-  <si>
     <t>Sigilo de Empresa em Situação Falimentar (Art. 169 da Lei nº 11.101/2005)</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>Serviços: Adestramento</t>
   </si>
   <si>
     <t>Processo relacionado a adestramento.</t>
   </si>
   <si>
-    <t>041.13</t>
-  </si>
-  <si>
     <t>Segredo de Justiça no Processo Penal (Art. 201, § 6º, do Código de Processo Penal)</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>Aquisições: Material De Consumo</t>
   </si>
   <si>
     <t>Processo relacionado a material de consumo.</t>
   </si>
   <si>
-    <t>033.22</t>
-  </si>
-  <si>
     <t>Livros e Registros Contábeis Empresariais (Art. 1.190 do Código Civil)</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Capacitação: Contratação de curso com ônus limitado à Instituição</t>
   </si>
   <si>
     <t>Processo relacionado a com ônus limitado.</t>
   </si>
   <si>
-    <t>028.12</t>
-  </si>
-  <si>
     <t>Sigilo do Inquérito Policial (Art. 20 do Código de Processo Penal)</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>Pessoal: Licenças</t>
   </si>
   <si>
     <t>Processo relacionado a licenças.</t>
   </si>
   <si>
-    <t>023.3</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>Pessoal: Direitos e Prerrogativas</t>
   </si>
   <si>
     <t>Processo relacionado a direitos e prerrogativas.</t>
   </si>
   <si>
-    <t>023.9</t>
-  </si>
-  <si>
     <t>U</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>Gestão de Patrimônio: Tombamento</t>
   </si>
   <si>
     <t>Processo relacionado a tombamento.</t>
   </si>
   <si>
-    <t>044.2</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>Pessoal: Outros Direitos Remuneratórios Na Ativa</t>
   </si>
   <si>
     <t>Processo relacionado a outros direitos remuneratórios na ativa.</t>
   </si>
   <si>
-    <t>023.19</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>Contabilidade: Gestão De Contas Especiais</t>
   </si>
   <si>
     <t>Processo relacionado a gestão de contas especiais.</t>
   </si>
   <si>
-    <t>053.3</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>Pessoal: Processo De Transferência Para a Reserva Remunerada</t>
   </si>
   <si>
     <t>Processo relacionado a processo de transferência para a reserva remunerada.</t>
   </si>
   <si>
-    <t>042.72</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>Gestão e Controle: Gestão Jurídica</t>
   </si>
   <si>
     <t>Processo relacionado a jurídica.</t>
   </si>
   <si>
-    <t>004.22</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>Capacitação: Designação, Matrícula, Conclusão, Cancelamento etc.</t>
   </si>
   <si>
     <t>Processo relacionado a designação, matrícula, conclusão, cancelamento, trancamento e/ou desligamento dos cursos.</t>
   </si>
   <si>
-    <t>024.32</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>Capacitação: Inscrição</t>
   </si>
   <si>
     <t>Processo relacionado a inscrição.</t>
   </si>
   <si>
-    <t>021.2</t>
-  </si>
-  <si>
     <t>Investigação Preliminar sobre Mercado Mobiliário (Art. 9º, § 2º, da Lei 6.385/1976)</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>Gestão de Processos: Modelagem De Processos</t>
   </si>
   <si>
     <t>Processo relacionado a modelagem de processos.</t>
   </si>
   <si>
-    <t>016.4</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>Pessoal: Solicitação de Licença Não Remunerada</t>
   </si>
   <si>
@@ -350,16 +236,10 @@
     <t>Segredo de Justiça no Processo Civil (Art. 189 do Código de Processo Civil)</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>Segurança do Trabalho: Constituição Da Comissão Interna De Prevenção De Acidentes (Cipa)</t>
   </si>
   <si>
     <t>Processo relacionado a constituição da comissão interna de prevenção de acidentes (cipa).</t>
-  </si>
-  <si>
-    <t>025.311</t>
   </si>
 </sst>
 </file>
@@ -746,33 +626,33 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="D2" s="0">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="E2" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="F2" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="G2" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="H2" s="0" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>21</v>
       </c>
       <c r="I2" s="0"/>
       <c r="J2" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K2" s="0"/>
       <c r="L2" s="0"/>
@@ -780,33 +660,33 @@
       <c r="N2" s="0"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="0" t="s">
-        <v>23</v>
+      <c r="A3" s="0">
+        <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D3" s="0">
+        <v>30.02</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" s="0"/>
       <c r="G3" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K3" s="0"/>
       <c r="L3" s="0"/>
@@ -814,25 +694,25 @@
       <c r="N3" s="0"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="0" t="s">
-        <v>31</v>
+      <c r="A4" s="0">
+        <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>34</v>
+        <v>28</v>
+      </c>
+      <c r="D4" s="0">
+        <v>28.21</v>
       </c>
       <c r="E4" s="0"/>
       <c r="F4" s="0"/>
       <c r="G4" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I4" s="0"/>
       <c r="J4" s="0"/>
@@ -842,99 +722,99 @@
       <c r="N4" s="0"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="0" t="s">
-        <v>36</v>
+      <c r="A5" s="0">
+        <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>39</v>
+        <v>31</v>
+      </c>
+      <c r="D5" s="0">
+        <v>23.155</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I5" s="0"/>
       <c r="J5" s="0" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M5" s="0"/>
       <c r="N5" s="0"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="0" t="s">
-        <v>44</v>
+      <c r="A6" s="0">
+        <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>47</v>
+        <v>36</v>
+      </c>
+      <c r="D6" s="0">
+        <v>914</v>
       </c>
       <c r="E6" s="0"/>
       <c r="F6" s="0"/>
       <c r="G6" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I6" s="0"/>
       <c r="J6" s="0" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="L6" s="0"/>
       <c r="M6" s="0"/>
       <c r="N6" s="0"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="0" t="s">
-        <v>49</v>
+      <c r="A7" s="0">
+        <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>52</v>
+        <v>39</v>
+      </c>
+      <c r="D7" s="0">
+        <v>41.13</v>
       </c>
       <c r="E7" s="0"/>
       <c r="F7" s="0"/>
       <c r="G7" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I7" s="0"/>
       <c r="J7" s="0" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K7" s="0"/>
       <c r="L7" s="0"/>
@@ -942,29 +822,29 @@
       <c r="N7" s="0"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="0" t="s">
-        <v>54</v>
+      <c r="A8" s="0">
+        <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>57</v>
+        <v>42</v>
+      </c>
+      <c r="D8" s="0">
+        <v>33.22</v>
       </c>
       <c r="E8" s="0"/>
       <c r="F8" s="0"/>
       <c r="G8" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I8" s="0"/>
       <c r="J8" s="0" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="K8" s="0"/>
       <c r="L8" s="0"/>
@@ -972,63 +852,63 @@
       <c r="N8" s="0"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="0" t="s">
-        <v>59</v>
+      <c r="A9" s="0">
+        <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>62</v>
+        <v>45</v>
+      </c>
+      <c r="D9" s="0">
+        <v>28.12</v>
       </c>
       <c r="E9" s="0"/>
       <c r="F9" s="0"/>
       <c r="G9" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I9" s="0"/>
       <c r="J9" s="0" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="K9" s="0"/>
       <c r="L9" s="0"/>
       <c r="M9" s="0" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="N9" s="0"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="0" t="s">
-        <v>64</v>
+      <c r="A10" s="0">
+        <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>67</v>
+        <v>48</v>
+      </c>
+      <c r="D10" s="0">
+        <v>23.3</v>
       </c>
       <c r="E10" s="0"/>
       <c r="F10" s="0"/>
       <c r="G10" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K10" s="0"/>
       <c r="L10" s="0"/>
@@ -1036,31 +916,31 @@
       <c r="N10" s="0"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="0" t="s">
-        <v>69</v>
+      <c r="A11" s="0">
+        <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>72</v>
+        <v>51</v>
+      </c>
+      <c r="D11" s="0">
+        <v>23.9</v>
       </c>
       <c r="E11" s="0"/>
       <c r="F11" s="0"/>
       <c r="G11" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K11" s="0"/>
       <c r="L11" s="0"/>
@@ -1068,25 +948,25 @@
       <c r="N11" s="0"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="0" t="s">
-        <v>74</v>
+      <c r="A12" s="0">
+        <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="D12" s="0">
+        <v>44.2</v>
       </c>
       <c r="E12" s="0"/>
       <c r="F12" s="0"/>
       <c r="G12" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
@@ -1094,33 +974,33 @@
       <c r="L12" s="0"/>
       <c r="M12" s="0"/>
       <c r="N12" s="0" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="0" t="s">
-        <v>78</v>
+      <c r="A13" s="0">
+        <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>81</v>
+        <v>56</v>
+      </c>
+      <c r="D13" s="0">
+        <v>23.19</v>
       </c>
       <c r="E13" s="0"/>
       <c r="F13" s="0"/>
       <c r="G13" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I13" s="0"/>
       <c r="J13" s="0" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K13" s="0"/>
       <c r="L13" s="0"/>
@@ -1128,25 +1008,25 @@
       <c r="N13" s="0"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="0" t="s">
-        <v>82</v>
+      <c r="A14" s="0">
+        <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>85</v>
+        <v>58</v>
+      </c>
+      <c r="D14" s="0">
+        <v>53.3</v>
       </c>
       <c r="E14" s="0"/>
       <c r="F14" s="0"/>
       <c r="G14" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I14" s="0"/>
       <c r="J14" s="0"/>
@@ -1156,29 +1036,29 @@
       <c r="N14" s="0"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="0" t="s">
-        <v>86</v>
+      <c r="A15" s="0">
+        <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>89</v>
+        <v>60</v>
+      </c>
+      <c r="D15" s="0">
+        <v>42.72</v>
       </c>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I15" s="0"/>
       <c r="J15" s="0" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
@@ -1186,25 +1066,25 @@
       <c r="N15" s="0"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="0" t="s">
-        <v>90</v>
+      <c r="A16" s="0">
+        <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>93</v>
+        <v>62</v>
+      </c>
+      <c r="D16" s="0">
+        <v>4.22</v>
       </c>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I16" s="0"/>
       <c r="J16" s="0"/>
@@ -1214,25 +1094,25 @@
       <c r="N16" s="0"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="0" t="s">
-        <v>94</v>
+      <c r="A17" s="0">
+        <v>16</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>97</v>
+        <v>64</v>
+      </c>
+      <c r="D17" s="0">
+        <v>24.32</v>
       </c>
       <c r="E17" s="0"/>
       <c r="F17" s="0"/>
       <c r="G17" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I17" s="0"/>
       <c r="J17" s="0"/>
@@ -1242,29 +1122,29 @@
       <c r="N17" s="0"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="0" t="s">
-        <v>98</v>
+      <c r="A18" s="0">
+        <v>17</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>101</v>
+        <v>66</v>
+      </c>
+      <c r="D18" s="0">
+        <v>21.2</v>
       </c>
       <c r="E18" s="0"/>
       <c r="F18" s="0"/>
       <c r="G18" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I18" s="0"/>
       <c r="J18" s="0" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
@@ -1272,25 +1152,25 @@
       <c r="N18" s="0"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="0" t="s">
-        <v>103</v>
+      <c r="A19" s="0">
+        <v>18</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>106</v>
+        <v>69</v>
+      </c>
+      <c r="D19" s="0">
+        <v>16.4</v>
       </c>
       <c r="E19" s="0"/>
       <c r="F19" s="0"/>
       <c r="G19" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I19" s="0"/>
       <c r="J19" s="0"/>
@@ -1300,29 +1180,29 @@
       <c r="N19" s="0"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="0" t="s">
-        <v>107</v>
+      <c r="A20" s="0">
+        <v>19</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="D20" s="0">
+        <v>23.3</v>
       </c>
       <c r="E20" s="0"/>
       <c r="F20" s="0"/>
       <c r="G20" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I20" s="0"/>
       <c r="J20" s="0" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
@@ -1330,25 +1210,25 @@
       <c r="N20" s="0"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="0" t="s">
-        <v>111</v>
+      <c r="A21" s="0">
+        <v>20</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>114</v>
+        <v>74</v>
+      </c>
+      <c r="D21" s="0">
+        <v>25.311</v>
       </c>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I21" s="0"/>
       <c r="J21" s="0"/>

--- a/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploTiposDeProcesso.xlsx
+++ b/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploTiposDeProcesso.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="114">
   <si>
     <t>0.Seq</t>
   </si>
@@ -59,12 +59,18 @@
     <t>13.InternoDoSistema</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Comunicação: Serviço De Transmissão De Dados, Voz E Imagem</t>
   </si>
   <si>
     <t>Processo relacionado a serviço de transmissão de dados, voz e imagem.</t>
   </si>
   <si>
+    <t>073.4</t>
+  </si>
+  <si>
     <t>ABC</t>
   </si>
   <si>
@@ -80,12 +86,18 @@
     <t>Protocolo Pendente de Análise de Restrição (Art. 6º, III, da Lei nº 12.527/2011)</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Gestão de Contrato: Cadastramento De Fornecedores E De Prestadores De Serviços</t>
   </si>
   <si>
     <t>Processo relacionado a cadastramento de fornecedores e de prestadores de serviços.</t>
   </si>
   <si>
+    <t>030.02</t>
+  </si>
+  <si>
     <t>PUB;RES;SIG</t>
   </si>
   <si>
@@ -95,7 +107,10 @@
     <t>R</t>
   </si>
   <si>
-    <t>Informação Pessoal Sensível (Art. 31 da Lei nº 12.527/2011)</t>
+    <t>Informação Pessoal (Art. 31 da Lei nº 12.527/2011)</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>Capacitação: Contratação de curso com ônus à Instituição</t>
@@ -104,15 +119,24 @@
     <t>Processo relacionado a com ônus.</t>
   </si>
   <si>
+    <t>028.21</t>
+  </si>
+  <si>
     <t>PUB</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>Pessoal: Avaliação de Desempenho</t>
   </si>
   <si>
     <t>Processo relacionado a desempenho.</t>
   </si>
   <si>
+    <t>023.155</t>
+  </si>
+  <si>
     <t>ABC:GABIN</t>
   </si>
   <si>
@@ -122,111 +146,198 @@
     <t>SIM</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>Pessoal: Emissão De Certificados</t>
   </si>
   <si>
     <t>Processo relacionado a emissão de certificados.</t>
   </si>
   <si>
+    <t>914</t>
+  </si>
+  <si>
     <t>Sigilo de Empresa em Situação Falimentar (Art. 169 da Lei nº 11.101/2005)</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>Serviços: Adestramento</t>
   </si>
   <si>
     <t>Processo relacionado a adestramento.</t>
   </si>
   <si>
+    <t>041.13</t>
+  </si>
+  <si>
     <t>Segredo de Justiça no Processo Penal (Art. 201, § 6º, do Código de Processo Penal)</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>Aquisições: Material De Consumo</t>
   </si>
   <si>
     <t>Processo relacionado a material de consumo.</t>
   </si>
   <si>
+    <t>033.22</t>
+  </si>
+  <si>
     <t>Livros e Registros Contábeis Empresariais (Art. 1.190 do Código Civil)</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>Capacitação: Contratação de curso com ônus limitado à Instituição</t>
   </si>
   <si>
     <t>Processo relacionado a com ônus limitado.</t>
   </si>
   <si>
+    <t>028.12</t>
+  </si>
+  <si>
     <t>Sigilo do Inquérito Policial (Art. 20 do Código de Processo Penal)</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>Pessoal: Licenças</t>
   </si>
   <si>
     <t>Processo relacionado a licenças.</t>
   </si>
   <si>
+    <t>023.3</t>
+  </si>
+  <si>
     <t>S</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>Pessoal: Direitos e Prerrogativas</t>
   </si>
   <si>
     <t>Processo relacionado a direitos e prerrogativas.</t>
   </si>
   <si>
+    <t>023.5</t>
+  </si>
+  <si>
     <t>U</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>Gestão de Patrimônio: Tombamento</t>
   </si>
   <si>
     <t>Processo relacionado a tombamento.</t>
   </si>
   <si>
+    <t>044.2</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>Pessoal: Outros Direitos Remuneratórios Na Ativa</t>
   </si>
   <si>
     <t>Processo relacionado a outros direitos remuneratórios na ativa.</t>
   </si>
   <si>
+    <t>023.191</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>Contabilidade: Gestão De Contas Especiais</t>
   </si>
   <si>
     <t>Processo relacionado a gestão de contas especiais.</t>
   </si>
   <si>
+    <t>053.3</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>Pessoal: Processo De Transferência Para a Reserva Remunerada</t>
   </si>
   <si>
     <t>Processo relacionado a processo de transferência para a reserva remunerada.</t>
   </si>
   <si>
+    <t>042.72</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Gestão e Controle: Gestão Jurídica</t>
   </si>
   <si>
     <t>Processo relacionado a jurídica.</t>
   </si>
   <si>
+    <t>004.22</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>Capacitação: Designação, Matrícula, Conclusão, Cancelamento etc.</t>
   </si>
   <si>
     <t>Processo relacionado a designação, matrícula, conclusão, cancelamento, trancamento e/ou desligamento dos cursos.</t>
   </si>
   <si>
+    <t>024.32</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>Capacitação: Inscrição</t>
   </si>
   <si>
     <t>Processo relacionado a inscrição.</t>
   </si>
   <si>
+    <t>021.2</t>
+  </si>
+  <si>
     <t>Investigação Preliminar sobre Mercado Mobiliário (Art. 9º, § 2º, da Lei 6.385/1976)</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>Gestão de Processos: Modelagem De Processos</t>
   </si>
   <si>
     <t>Processo relacionado a modelagem de processos.</t>
   </si>
   <si>
+    <t>016.4</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>Pessoal: Solicitação de Licença Não Remunerada</t>
   </si>
   <si>
@@ -236,10 +347,16 @@
     <t>Segredo de Justiça no Processo Civil (Art. 189 do Código de Processo Civil)</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>Segurança do Trabalho: Constituição Da Comissão Interna De Prevenção De Acidentes (Cipa)</t>
   </si>
   <si>
     <t>Processo relacionado a constituição da comissão interna de prevenção de acidentes (cipa).</t>
+  </si>
+  <si>
+    <t>025.311</t>
   </si>
 </sst>
 </file>
@@ -626,33 +743,33 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="0">
-        <v>1</v>
+      <c r="A2" s="0" t="s">
+        <v>14</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="0">
-        <v>73.40000000000001</v>
+        <v>16</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>17</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2" s="0"/>
       <c r="J2" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" s="0"/>
       <c r="L2" s="0"/>
@@ -660,33 +777,33 @@
       <c r="N2" s="0"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="0">
-        <v>2</v>
+      <c r="A3" s="0" t="s">
+        <v>23</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="0">
-        <v>30.02</v>
+        <v>25</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>26</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="0"/>
       <c r="G3" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K3" s="0"/>
       <c r="L3" s="0"/>
@@ -694,25 +811,25 @@
       <c r="N3" s="0"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="0">
-        <v>3</v>
+      <c r="A4" s="0" t="s">
+        <v>31</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="0">
-        <v>28.21</v>
+        <v>33</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="E4" s="0"/>
       <c r="F4" s="0"/>
       <c r="G4" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I4" s="0"/>
       <c r="J4" s="0"/>
@@ -722,99 +839,99 @@
       <c r="N4" s="0"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="0">
-        <v>4</v>
+      <c r="A5" s="0" t="s">
+        <v>36</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="0">
-        <v>23.155</v>
+        <v>38</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>39</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I5" s="0"/>
       <c r="J5" s="0" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M5" s="0"/>
       <c r="N5" s="0"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="0">
-        <v>5</v>
+      <c r="A6" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="0">
-        <v>914</v>
+        <v>45</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>46</v>
       </c>
       <c r="E6" s="0"/>
       <c r="F6" s="0"/>
       <c r="G6" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6" s="0"/>
       <c r="J6" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L6" s="0"/>
       <c r="M6" s="0"/>
       <c r="N6" s="0"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="0">
-        <v>6</v>
+      <c r="A7" s="0" t="s">
+        <v>48</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="0">
-        <v>41.13</v>
+        <v>50</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>51</v>
       </c>
       <c r="E7" s="0"/>
       <c r="F7" s="0"/>
       <c r="G7" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I7" s="0"/>
       <c r="J7" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="K7" s="0"/>
       <c r="L7" s="0"/>
@@ -822,29 +939,29 @@
       <c r="N7" s="0"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="0">
-        <v>7</v>
+      <c r="A8" s="0" t="s">
+        <v>53</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="0">
-        <v>33.22</v>
+        <v>55</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>56</v>
       </c>
       <c r="E8" s="0"/>
       <c r="F8" s="0"/>
       <c r="G8" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I8" s="0"/>
       <c r="J8" s="0" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K8" s="0"/>
       <c r="L8" s="0"/>
@@ -852,63 +969,63 @@
       <c r="N8" s="0"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="0">
-        <v>8</v>
+      <c r="A9" s="0" t="s">
+        <v>58</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="0">
-        <v>28.12</v>
+        <v>60</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>61</v>
       </c>
       <c r="E9" s="0"/>
       <c r="F9" s="0"/>
       <c r="G9" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I9" s="0"/>
       <c r="J9" s="0" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K9" s="0"/>
       <c r="L9" s="0"/>
       <c r="M9" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N9" s="0"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="0">
-        <v>9</v>
+      <c r="A10" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="0">
-        <v>23.3</v>
+        <v>65</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="E10" s="0"/>
       <c r="F10" s="0"/>
       <c r="G10" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K10" s="0"/>
       <c r="L10" s="0"/>
@@ -916,31 +1033,31 @@
       <c r="N10" s="0"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="0">
-        <v>10</v>
+      <c r="A11" s="0" t="s">
+        <v>68</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="0">
-        <v>23.9</v>
+        <v>70</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>71</v>
       </c>
       <c r="E11" s="0"/>
       <c r="F11" s="0"/>
       <c r="G11" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K11" s="0"/>
       <c r="L11" s="0"/>
@@ -948,25 +1065,25 @@
       <c r="N11" s="0"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="0">
-        <v>11</v>
+      <c r="A12" s="0" t="s">
+        <v>73</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="0">
-        <v>44.2</v>
+        <v>75</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>76</v>
       </c>
       <c r="E12" s="0"/>
       <c r="F12" s="0"/>
       <c r="G12" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
@@ -974,33 +1091,33 @@
       <c r="L12" s="0"/>
       <c r="M12" s="0"/>
       <c r="N12" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="0">
-        <v>12</v>
+      <c r="A13" s="0" t="s">
+        <v>77</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="0">
-        <v>23.19</v>
+        <v>79</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>80</v>
       </c>
       <c r="E13" s="0"/>
       <c r="F13" s="0"/>
       <c r="G13" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I13" s="0"/>
       <c r="J13" s="0" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K13" s="0"/>
       <c r="L13" s="0"/>
@@ -1008,25 +1125,25 @@
       <c r="N13" s="0"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="0">
-        <v>13</v>
+      <c r="A14" s="0" t="s">
+        <v>81</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="0">
-        <v>53.3</v>
+        <v>83</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>84</v>
       </c>
       <c r="E14" s="0"/>
       <c r="F14" s="0"/>
       <c r="G14" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I14" s="0"/>
       <c r="J14" s="0"/>
@@ -1036,29 +1153,29 @@
       <c r="N14" s="0"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="0">
-        <v>14</v>
+      <c r="A15" s="0" t="s">
+        <v>85</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="0">
-        <v>42.72</v>
+        <v>87</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>88</v>
       </c>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I15" s="0"/>
       <c r="J15" s="0" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
@@ -1066,25 +1183,25 @@
       <c r="N15" s="0"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="0">
-        <v>15</v>
+      <c r="A16" s="0" t="s">
+        <v>89</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="0">
-        <v>4.22</v>
+        <v>91</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>92</v>
       </c>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I16" s="0"/>
       <c r="J16" s="0"/>
@@ -1094,25 +1211,25 @@
       <c r="N16" s="0"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="0">
-        <v>16</v>
+      <c r="A17" s="0" t="s">
+        <v>93</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="0">
-        <v>24.32</v>
+        <v>95</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>96</v>
       </c>
       <c r="E17" s="0"/>
       <c r="F17" s="0"/>
       <c r="G17" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I17" s="0"/>
       <c r="J17" s="0"/>
@@ -1122,29 +1239,29 @@
       <c r="N17" s="0"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="0">
-        <v>17</v>
+      <c r="A18" s="0" t="s">
+        <v>97</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="0">
-        <v>21.2</v>
+        <v>99</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>100</v>
       </c>
       <c r="E18" s="0"/>
       <c r="F18" s="0"/>
       <c r="G18" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I18" s="0"/>
       <c r="J18" s="0" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
@@ -1152,25 +1269,25 @@
       <c r="N18" s="0"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="0">
-        <v>18</v>
+      <c r="A19" s="0" t="s">
+        <v>102</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="0">
-        <v>16.4</v>
+        <v>104</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>105</v>
       </c>
       <c r="E19" s="0"/>
       <c r="F19" s="0"/>
       <c r="G19" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I19" s="0"/>
       <c r="J19" s="0"/>
@@ -1180,29 +1297,29 @@
       <c r="N19" s="0"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="0">
-        <v>19</v>
+      <c r="A20" s="0" t="s">
+        <v>106</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="0">
-        <v>23.3</v>
+        <v>108</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>66</v>
       </c>
       <c r="E20" s="0"/>
       <c r="F20" s="0"/>
       <c r="G20" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I20" s="0"/>
       <c r="J20" s="0" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
@@ -1210,25 +1327,25 @@
       <c r="N20" s="0"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="0">
-        <v>20</v>
+      <c r="A21" s="0" t="s">
+        <v>110</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="0">
-        <v>25.311</v>
+        <v>112</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>113</v>
       </c>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I21" s="0"/>
       <c r="J21" s="0"/>
